--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-organization.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T10:31:14+00:00</t>
+    <t>2026-02-04T11:03:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-organization.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T11:03:32+00:00</t>
+    <t>2026-02-06T08:16:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-organization.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T08:16:26+00:00</t>
+    <t>2026-02-06T09:56:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-organization.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-organization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5764" uniqueCount="613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5764" uniqueCount="614">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T09:56:58+00:00</t>
+    <t>2026-02-06T10:49:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,7 +111,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -439,7 +439,7 @@
     <t>Organization.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+    <t xml:space="preserve">canonical(StructureDefinition)
 </t>
   </si>
   <si>
@@ -490,7 +490,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -514,7 +514,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -557,7 +557,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -633,7 +633,7 @@
     <t>shortName</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-short-name|2.1.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-short-name}
 </t>
   </si>
   <si>
@@ -650,7 +650,7 @@
     <t>description</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-description|2.1.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-description}
 </t>
   </si>
   <si>
@@ -663,7 +663,7 @@
     <t>usePeriod</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {organization-period|5.2.0}
+    <t xml:space="preserve">Extension {organization-period}
 </t>
   </si>
   <si>
@@ -749,7 +749,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use</t>
   </si>
   <si>
     <t>Identifier.use</t>
@@ -777,7 +777,7 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-organization-identifier-type|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-organization-identifier-type</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -871,7 +871,7 @@
     <t>Organization.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
+    <t xml:space="preserve">Reference(Organization)
 </t>
   </si>
   <si>
@@ -921,6 +921,9 @@
   </si>
   <si>
     <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
   </si>
   <si>
     <t>Organization.identifier:idNatSt.type</t>
@@ -937,7 +940,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
   </si>
   <si>
     <t>Organization.identifier:idNatSt.system</t>
@@ -1421,7 +1424,7 @@
     <t>Used to categorize the organization.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/organization-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/organization-type</t>
   </si>
   <si>
     <t xml:space="preserve">pattern:$this}
@@ -1443,7 +1446,7 @@
     <t>organizationType</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-organization-type|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-organization-type</t>
   </si>
   <si>
     <t>Organization.type:organizationType.id</t>
@@ -1524,7 +1527,7 @@
     <t>Secteurs d'activité des établissements avec la même activité dans le RASS</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J101-SecteurActivite-RASS/FHIR/JDV-J101-SecteurActivite-RASS|20250828120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J101-SecteurActivite-RASS/FHIR/JDV-J101-SecteurActivite-RASS</t>
   </si>
   <si>
     <t>Organization.type:secteurActiviteRASS.id</t>
@@ -1569,7 +1572,7 @@
     <t>Catégorie d'établissement du RASS</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J129-CategorieEtablissement-RASS/FHIR/JDV-J129-CategorieEtablissement-RASS|20241025120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J129-CategorieEtablissement-RASS/FHIR/JDV-J129-CategorieEtablissement-RASS</t>
   </si>
   <si>
     <t>Organization.type:categorieEtablissementRASS.id</t>
@@ -1651,7 +1654,7 @@
     <t>Organization.telecom</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.1.0}
+    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point}
 </t>
   </si>
   <si>
@@ -1683,7 +1686,7 @@
     <t>Organization.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address|2.1.0}
+    <t xml:space="preserve">Address {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address}
 </t>
   </si>
   <si>
@@ -1715,7 +1718,7 @@
     <t>Organization.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.1.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
 </t>
   </si>
   <si>
@@ -1868,7 +1871,7 @@
     <t>The purpose for which you would contact a contact party.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/contactentity-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/contactentity-type</t>
   </si>
   <si>
     <t>./type</t>
@@ -1915,7 +1918,7 @@
     <t>Organization.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint|4.0.1)
+    <t xml:space="preserve">Reference(Endpoint)
 </t>
   </si>
   <si>
@@ -2240,7 +2243,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="75.71875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="71.19140625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2255,7 +2258,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="107.44921875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="92.91796875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -6321,7 +6324,7 @@
         <v>291</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>235</v>
+        <v>292</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>78</v>
@@ -6371,7 +6374,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>238</v>
@@ -6419,7 +6422,7 @@
         <v>78</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>78</v>
@@ -6437,10 +6440,10 @@
         <v>151</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>78</v>
@@ -6490,7 +6493,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>247</v>
@@ -6538,7 +6541,7 @@
         <v>78</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>252</v>
@@ -6609,7 +6612,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>257</v>
@@ -6638,7 +6641,7 @@
         <v>103</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M38" t="s" s="2">
         <v>259</v>
@@ -6726,7 +6729,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>266</v>
@@ -6841,7 +6844,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>274</v>
@@ -6958,13 +6961,13 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>215</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>78</v>
@@ -6989,7 +6992,7 @@
         <v>216</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M41" t="s" s="2">
         <v>218</v>
@@ -7077,7 +7080,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>227</v>
@@ -7192,7 +7195,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>228</v>
@@ -7309,7 +7312,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>229</v>
@@ -7378,7 +7381,7 @@
         <v>291</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>235</v>
+        <v>292</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>78</v>
@@ -7428,7 +7431,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>238</v>
@@ -7476,7 +7479,7 @@
         <v>78</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>78</v>
@@ -7494,10 +7497,10 @@
         <v>151</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>78</v>
@@ -7547,7 +7550,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>247</v>
@@ -7595,7 +7598,7 @@
         <v>78</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="T46" t="s" s="2">
         <v>252</v>
@@ -7666,7 +7669,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>257</v>
@@ -7783,7 +7786,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>266</v>
@@ -7898,7 +7901,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>274</v>
@@ -8015,13 +8018,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>215</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>78</v>
@@ -8046,7 +8049,7 @@
         <v>216</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M50" t="s" s="2">
         <v>218</v>
@@ -8134,7 +8137,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>227</v>
@@ -8249,7 +8252,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>228</v>
@@ -8366,7 +8369,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>229</v>
@@ -8435,7 +8438,7 @@
         <v>291</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>235</v>
+        <v>292</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>78</v>
@@ -8485,7 +8488,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>238</v>
@@ -8533,7 +8536,7 @@
         <v>78</v>
       </c>
       <c r="S54" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="T54" t="s" s="2">
         <v>78</v>
@@ -8551,10 +8554,10 @@
         <v>151</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>78</v>
@@ -8604,7 +8607,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>247</v>
@@ -8652,7 +8655,7 @@
         <v>78</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>252</v>
@@ -8723,7 +8726,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>257</v>
@@ -8840,7 +8843,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>266</v>
@@ -8955,7 +8958,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>274</v>
@@ -9072,13 +9075,13 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>215</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>78</v>
@@ -9103,7 +9106,7 @@
         <v>216</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M59" t="s" s="2">
         <v>218</v>
@@ -9191,7 +9194,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>227</v>
@@ -9306,7 +9309,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>228</v>
@@ -9423,7 +9426,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>229</v>
@@ -9492,7 +9495,7 @@
         <v>291</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>235</v>
+        <v>292</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>78</v>
@@ -9542,7 +9545,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>238</v>
@@ -9608,10 +9611,10 @@
         <v>151</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>78</v>
@@ -9661,10 +9664,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9776,10 +9779,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9893,10 +9896,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9922,16 +9925,16 @@
         <v>147</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>78</v>
@@ -9980,7 +9983,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9998,10 +10001,10 @@
         <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>78</v>
@@ -10012,10 +10015,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10127,10 +10130,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10244,10 +10247,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10273,16 +10276,16 @@
         <v>131</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>78</v>
@@ -10292,7 +10295,7 @@
         <v>78</v>
       </c>
       <c r="S69" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="T69" t="s" s="2">
         <v>78</v>
@@ -10331,7 +10334,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10349,10 +10352,10 @@
         <v>78</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>78</v>
@@ -10363,10 +10366,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10392,13 +10395,13 @@
         <v>103</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10448,7 +10451,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10466,10 +10469,10 @@
         <v>78</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>78</v>
@@ -10480,10 +10483,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10509,14 +10512,14 @@
         <v>169</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -10565,7 +10568,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10583,10 +10586,10 @@
         <v>78</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>78</v>
@@ -10597,10 +10600,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10626,14 +10629,14 @@
         <v>103</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>78</v>
@@ -10682,7 +10685,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10700,10 +10703,10 @@
         <v>78</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>78</v>
@@ -10714,10 +10717,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10740,19 +10743,19 @@
         <v>90</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>78</v>
@@ -10801,7 +10804,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10819,10 +10822,10 @@
         <v>78</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>78</v>
@@ -10833,10 +10836,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10862,16 +10865,16 @@
         <v>103</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>78</v>
@@ -10920,7 +10923,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10938,10 +10941,10 @@
         <v>78</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>78</v>
@@ -10952,7 +10955,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>247</v>
@@ -11000,7 +11003,7 @@
         <v>78</v>
       </c>
       <c r="S75" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="T75" t="s" s="2">
         <v>252</v>
@@ -11071,7 +11074,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>257</v>
@@ -11188,7 +11191,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>266</v>
@@ -11303,7 +11306,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>274</v>
@@ -11420,13 +11423,13 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>215</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>78</v>
@@ -11451,7 +11454,7 @@
         <v>216</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M79" t="s" s="2">
         <v>218</v>
@@ -11539,7 +11542,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>227</v>
@@ -11654,7 +11657,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>228</v>
@@ -11771,7 +11774,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>229</v>
@@ -11840,7 +11843,7 @@
         <v>291</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>235</v>
+        <v>292</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>78</v>
@@ -11890,7 +11893,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>238</v>
@@ -11938,7 +11941,7 @@
         <v>78</v>
       </c>
       <c r="S83" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="T83" t="s" s="2">
         <v>78</v>
@@ -11956,10 +11959,10 @@
         <v>151</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>78</v>
@@ -12009,7 +12012,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>247</v>
@@ -12057,7 +12060,7 @@
         <v>78</v>
       </c>
       <c r="S84" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="T84" t="s" s="2">
         <v>252</v>
@@ -12128,7 +12131,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>257</v>
@@ -12245,7 +12248,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>266</v>
@@ -12360,7 +12363,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>274</v>
@@ -12477,13 +12480,13 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>215</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>78</v>
@@ -12508,7 +12511,7 @@
         <v>216</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M88" t="s" s="2">
         <v>218</v>
@@ -12596,7 +12599,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>227</v>
@@ -12711,7 +12714,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>228</v>
@@ -12828,7 +12831,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>229</v>
@@ -12897,7 +12900,7 @@
         <v>291</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>235</v>
+        <v>292</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>78</v>
@@ -12947,7 +12950,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>238</v>
@@ -12995,7 +12998,7 @@
         <v>78</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>78</v>
@@ -13013,10 +13016,10 @@
         <v>151</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>78</v>
@@ -13066,7 +13069,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>247</v>
@@ -13114,7 +13117,7 @@
         <v>78</v>
       </c>
       <c r="S93" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="T93" t="s" s="2">
         <v>252</v>
@@ -13185,7 +13188,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>257</v>
@@ -13302,7 +13305,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>266</v>
@@ -13417,7 +13420,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>274</v>
@@ -13534,10 +13537,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13560,70 +13563,70 @@
         <v>90</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="P97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q97" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="R97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF97" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="P97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q97" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="R97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF97" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13641,24 +13644,24 @@
         <v>78</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13684,16 +13687,16 @@
         <v>239</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>78</v>
@@ -13721,16 +13724,16 @@
         <v>159</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AC98" s="2"/>
       <c r="AD98" t="s" s="2">
@@ -13740,7 +13743,7 @@
         <v>116</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -13758,27 +13761,27 @@
         <v>78</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>78</v>
@@ -13803,16 +13806,16 @@
         <v>239</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>78</v>
@@ -13841,7 +13844,7 @@
       </c>
       <c r="Y99" s="2"/>
       <c r="Z99" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>78</v>
@@ -13859,7 +13862,7 @@
         <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -13877,24 +13880,24 @@
         <v>78</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14006,10 +14009,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14123,10 +14126,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14152,16 +14155,16 @@
         <v>147</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>78</v>
@@ -14210,7 +14213,7 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -14228,10 +14231,10 @@
         <v>78</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>78</v>
@@ -14242,10 +14245,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14357,10 +14360,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14474,10 +14477,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14503,16 +14506,16 @@
         <v>131</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>78</v>
@@ -14561,7 +14564,7 @@
         <v>78</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -14579,10 +14582,10 @@
         <v>78</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>78</v>
@@ -14593,10 +14596,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14622,13 +14625,13 @@
         <v>103</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -14678,7 +14681,7 @@
         <v>78</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -14696,10 +14699,10 @@
         <v>78</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>78</v>
@@ -14710,10 +14713,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14739,14 +14742,14 @@
         <v>169</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>78</v>
@@ -14795,7 +14798,7 @@
         <v>78</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -14813,10 +14816,10 @@
         <v>78</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>78</v>
@@ -14827,10 +14830,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14856,14 +14859,14 @@
         <v>103</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>78</v>
@@ -14912,7 +14915,7 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -14930,10 +14933,10 @@
         <v>78</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>78</v>
@@ -14944,10 +14947,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14970,19 +14973,19 @@
         <v>90</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>78</v>
@@ -15031,7 +15034,7 @@
         <v>78</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -15049,10 +15052,10 @@
         <v>78</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>78</v>
@@ -15063,10 +15066,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15092,16 +15095,16 @@
         <v>103</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>78</v>
@@ -15150,7 +15153,7 @@
         <v>78</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -15168,10 +15171,10 @@
         <v>78</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>78</v>
@@ -15182,13 +15185,13 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>78</v>
@@ -15213,16 +15216,16 @@
         <v>239</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>78</v>
@@ -15251,7 +15254,7 @@
       </c>
       <c r="Y111" s="2"/>
       <c r="Z111" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>78</v>
@@ -15269,7 +15272,7 @@
         <v>78</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -15287,24 +15290,24 @@
         <v>78</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15416,10 +15419,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15533,10 +15536,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15562,16 +15565,16 @@
         <v>147</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>78</v>
@@ -15620,7 +15623,7 @@
         <v>78</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
@@ -15638,10 +15641,10 @@
         <v>78</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>78</v>
@@ -15652,10 +15655,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15767,10 +15770,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15884,10 +15887,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15913,16 +15916,16 @@
         <v>131</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>78</v>
@@ -15971,7 +15974,7 @@
         <v>78</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
@@ -15989,10 +15992,10 @@
         <v>78</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>78</v>
@@ -16003,10 +16006,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16032,13 +16035,13 @@
         <v>103</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -16088,7 +16091,7 @@
         <v>78</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
@@ -16106,10 +16109,10 @@
         <v>78</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>78</v>
@@ -16120,10 +16123,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16149,14 +16152,14 @@
         <v>169</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>78</v>
@@ -16205,7 +16208,7 @@
         <v>78</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -16223,10 +16226,10 @@
         <v>78</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>78</v>
@@ -16237,10 +16240,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16266,14 +16269,14 @@
         <v>103</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>78</v>
@@ -16322,7 +16325,7 @@
         <v>78</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -16340,10 +16343,10 @@
         <v>78</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>78</v>
@@ -16354,10 +16357,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16380,19 +16383,19 @@
         <v>90</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>78</v>
@@ -16441,7 +16444,7 @@
         <v>78</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -16459,10 +16462,10 @@
         <v>78</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>78</v>
@@ -16473,10 +16476,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16502,16 +16505,16 @@
         <v>103</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>78</v>
@@ -16560,7 +16563,7 @@
         <v>78</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -16578,10 +16581,10 @@
         <v>78</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>78</v>
@@ -16592,13 +16595,13 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D123" t="s" s="2">
         <v>78</v>
@@ -16623,16 +16626,16 @@
         <v>239</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>78</v>
@@ -16661,7 +16664,7 @@
       </c>
       <c r="Y123" s="2"/>
       <c r="Z123" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>78</v>
@@ -16679,7 +16682,7 @@
         <v>78</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -16697,24 +16700,24 @@
         <v>78</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO123" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16826,10 +16829,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16943,10 +16946,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16972,16 +16975,16 @@
         <v>147</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>78</v>
@@ -17030,7 +17033,7 @@
         <v>78</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -17048,10 +17051,10 @@
         <v>78</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>78</v>
@@ -17062,10 +17065,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17177,10 +17180,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17294,10 +17297,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17323,16 +17326,16 @@
         <v>131</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>78</v>
@@ -17381,7 +17384,7 @@
         <v>78</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
@@ -17399,10 +17402,10 @@
         <v>78</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>78</v>
@@ -17413,10 +17416,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17442,13 +17445,13 @@
         <v>103</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
@@ -17498,7 +17501,7 @@
         <v>78</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
@@ -17516,10 +17519,10 @@
         <v>78</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AN130" t="s" s="2">
         <v>78</v>
@@ -17530,10 +17533,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17559,14 +17562,14 @@
         <v>169</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>78</v>
@@ -17615,7 +17618,7 @@
         <v>78</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
@@ -17633,10 +17636,10 @@
         <v>78</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>78</v>
@@ -17647,10 +17650,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17676,14 +17679,14 @@
         <v>103</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>78</v>
@@ -17732,7 +17735,7 @@
         <v>78</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
@@ -17750,10 +17753,10 @@
         <v>78</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AN132" t="s" s="2">
         <v>78</v>
@@ -17764,10 +17767,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17790,19 +17793,19 @@
         <v>90</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>78</v>
@@ -17851,7 +17854,7 @@
         <v>78</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -17869,10 +17872,10 @@
         <v>78</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>78</v>
@@ -17883,10 +17886,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17912,16 +17915,16 @@
         <v>103</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>78</v>
@@ -17970,7 +17973,7 @@
         <v>78</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -17988,10 +17991,10 @@
         <v>78</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>78</v>
@@ -18002,10 +18005,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18031,16 +18034,16 @@
         <v>103</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>78</v>
@@ -18089,7 +18092,7 @@
         <v>78</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -18104,16 +18107,16 @@
         <v>101</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>78</v>
@@ -18121,10 +18124,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18150,16 +18153,16 @@
         <v>103</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>78</v>
@@ -18208,7 +18211,7 @@
         <v>78</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -18229,7 +18232,7 @@
         <v>78</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>78</v>
@@ -18240,10 +18243,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18266,19 +18269,19 @@
         <v>78</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>78</v>
@@ -18327,7 +18330,7 @@
         <v>78</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
@@ -18339,19 +18342,19 @@
         <v>201</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AK137" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AO137" t="s" s="2">
         <v>78</v>
@@ -18359,10 +18362,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18385,19 +18388,19 @@
         <v>78</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>78</v>
@@ -18446,7 +18449,7 @@
         <v>78</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>79</v>
@@ -18458,19 +18461,19 @@
         <v>201</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AK138" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AO138" t="s" s="2">
         <v>78</v>
@@ -18478,10 +18481,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18504,17 +18507,17 @@
         <v>90</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>78</v>
@@ -18563,7 +18566,7 @@
         <v>78</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>79</v>
@@ -18581,10 +18584,10 @@
         <v>78</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AN139" t="s" s="2">
         <v>107</v>
@@ -18595,10 +18598,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18710,10 +18713,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18827,10 +18830,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18856,13 +18859,13 @@
         <v>103</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
@@ -18912,7 +18915,7 @@
         <v>78</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
@@ -18921,7 +18924,7 @@
         <v>89</v>
       </c>
       <c r="AI142" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AJ142" t="s" s="2">
         <v>101</v>
@@ -18944,10 +18947,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18973,13 +18976,13 @@
         <v>131</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
@@ -19009,7 +19012,7 @@
       </c>
       <c r="Y143" s="2"/>
       <c r="Z143" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AA143" t="s" s="2">
         <v>78</v>
@@ -19027,7 +19030,7 @@
         <v>78</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -19059,10 +19062,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19088,13 +19091,13 @@
         <v>216</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -19144,7 +19147,7 @@
         <v>78</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>79</v>
@@ -19165,7 +19168,7 @@
         <v>78</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AN144" t="s" s="2">
         <v>78</v>
@@ -19176,10 +19179,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19205,13 +19208,13 @@
         <v>103</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
@@ -19261,7 +19264,7 @@
         <v>78</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>79</v>
@@ -19293,10 +19296,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19319,19 +19322,19 @@
         <v>78</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>78</v>
@@ -19380,7 +19383,7 @@
         <v>78</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>79</v>
@@ -19401,7 +19404,7 @@
         <v>78</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AN146" t="s" s="2">
         <v>78</v>
@@ -19412,10 +19415,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19527,10 +19530,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19644,14 +19647,14 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" t="s" s="2">
@@ -19673,10 +19676,10 @@
         <v>110</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N149" t="s" s="2">
         <v>113</v>
@@ -19731,7 +19734,7 @@
         <v>78</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
@@ -19763,10 +19766,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -19792,14 +19795,14 @@
         <v>239</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>78</v>
@@ -19827,10 +19830,10 @@
         <v>151</v>
       </c>
       <c r="Y150" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="Z150" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>78</v>
@@ -19848,7 +19851,7 @@
         <v>78</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>79</v>
@@ -19869,7 +19872,7 @@
         <v>78</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AN150" t="s" s="2">
         <v>78</v>
@@ -19880,10 +19883,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -19906,17 +19909,17 @@
         <v>78</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>78</v>
@@ -19965,7 +19968,7 @@
         <v>78</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>79</v>
@@ -19983,10 +19986,10 @@
         <v>78</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AN151" t="s" s="2">
         <v>78</v>
@@ -19997,10 +20000,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20023,17 +20026,17 @@
         <v>78</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>78</v>
@@ -20082,7 +20085,7 @@
         <v>78</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>79</v>
@@ -20094,19 +20097,19 @@
         <v>201</v>
       </c>
       <c r="AJ152" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AK152" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AO152" t="s" s="2">
         <v>78</v>
@@ -20114,10 +20117,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20140,19 +20143,19 @@
         <v>78</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O153" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>78</v>
@@ -20201,7 +20204,7 @@
         <v>78</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>79</v>
@@ -20219,13 +20222,13 @@
         <v>78</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>78</v>
@@ -20233,10 +20236,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20259,17 +20262,17 @@
         <v>78</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>78</v>
@@ -20318,7 +20321,7 @@
         <v>78</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>79</v>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-organization.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T10:49:33+00:00</t>
+    <t>2026-02-10T10:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-organization.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-10T10:00:25+00:00</t>
+    <t>2026-02-11T15:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-organization.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T15:08:15+00:00</t>
+    <t>2026-02-12T14:50:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-organization.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-12T14:50:08+00:00</t>
+    <t>2026-02-16T09:17:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-organization.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T09:17:35+00:00</t>
+    <t>2026-02-16T09:32:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-organization.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T09:32:48+00:00</t>
+    <t>2026-02-16T14:58:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-organization.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T14:58:48+00:00</t>
+    <t>2026-02-23T15:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-organization.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T15:44:46+00:00</t>
+    <t>2026-02-24T10:21:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-organization.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-organization.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T10:21:42+00:00</t>
+    <t>2026-02-24T16:53:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-organization.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-organization.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T16:53:25+00:00</t>
+    <t>2026-02-25T09:45:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-organization.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-organization.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T09:45:56+00:00</t>
+    <t>2026-02-26T08:21:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-organization.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T08:21:36+00:00</t>
+    <t>2026-02-26T10:20:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
